--- a/public/plantilla_mercancia.xlsx
+++ b/public/plantilla_mercancia.xlsx
@@ -5,67 +5,45 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisi\OneDrive\Escritorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA7E99E-5A9D-402F-B52F-4299E93A6051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0080559-8B4C-4853-8B53-64285EA1B54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
-  <si>
-    <t>Fecha de compra</t>
-  </si>
-  <si>
-    <t>Descripción de la mercancía</t>
-  </si>
-  <si>
-    <t>Cantidad adquirida</t>
-  </si>
-  <si>
-    <t>Costo unitario</t>
-  </si>
-  <si>
-    <t>Costo total</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+  <si>
+    <t>Descripción del Producto</t>
+  </si>
+  <si>
+    <t>Cantidad</t>
+  </si>
+  <si>
+    <t>Costo Unitario</t>
   </si>
   <si>
     <t>Categoría</t>
   </si>
   <si>
-    <t>Método de pago</t>
+    <t>Método de Pago</t>
   </si>
   <si>
     <t>Observaciones</t>
   </si>
   <si>
-    <t>00/00/2025</t>
+    <t>Transferencia</t>
   </si>
   <si>
     <t>Ejemplo</t>
-  </si>
-  <si>
-    <t>efectivo, tarjeta o transferencia</t>
   </si>
 </sst>
 </file>
@@ -124,15 +102,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,14 +411,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -462,41 +433,33 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
+      <c r="B2">
+        <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <f>C2*D2</f>
-        <v>0</v>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{9C07D7B8-D086-4FF2-9B20-1FA245ADBC85}">
+      <formula1>"Transferencia, Efectivo, Tarjeta"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/plantilla_mercancia.xlsx
+++ b/public/plantilla_mercancia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisi\OneDrive\Escritorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0080559-8B4C-4853-8B53-64285EA1B54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F0BB30-6D8A-4D96-8071-A95CFC4AB834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -439,10 +439,10 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -455,9 +455,15 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{9C07D7B8-D086-4FF2-9B20-1FA245ADBC85}">
       <formula1>"Transferencia, Efectivo, Tarjeta"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{BBE1362C-36D9-4DC5-BA86-05C1F73C14E8}">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{2494649E-2341-407D-87A3-DDBC104B129B}">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/plantilla_mercancia.xlsx
+++ b/public/plantilla_mercancia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisi\OneDrive\Escritorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F0BB30-6D8A-4D96-8071-A95CFC4AB834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6759349C-92D4-47AD-8C48-5E4ABEF103D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>Descripción del Producto</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Método de Pago</t>
-  </si>
-  <si>
-    <t>Observaciones</t>
   </si>
   <si>
     <t>Transferencia</t>
@@ -411,10 +408,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -430,13 +427,10 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -445,13 +439,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
